--- a/log_parser/logoutput.xlsx
+++ b/log_parser/logoutput.xlsx
@@ -29,7 +29,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -38,8 +38,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FF0000"/>
+        <bgColor rgb="00FF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFFF00"/>
         <bgColor rgb="00FFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0033FF00"/>
+        <bgColor rgb="0033FF00"/>
       </patternFill>
     </fill>
     <fill>
@@ -61,10 +73,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,12 +459,12 @@
           <t>UVM_ERROR</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>UVM_WARNING</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>UVM_INFO</t>
         </is>
@@ -462,22 +476,22 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>TOTAL: 4</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>TOTAL: 4</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>TOTAL: 12</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>TOTAL: 2</t>
         </is>
